--- a/问题一/output/第一问_汇总分析与检验.xlsx
+++ b/问题一/output/第一问_汇总分析与检验.xlsx
@@ -444,7 +444,7 @@
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>result1已按自然时段重写行标签</t>
+          <t>官方模板标签保持不变；模型内部按自然时段计算</t>
         </is>
       </c>
     </row>
